--- a/AAII_Financials/Quarterly/ASTR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASTR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
   <si>
     <t>ASTR</t>
   </si>
@@ -1181,8 +1181,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>28900</v>
       </c>
       <c r="E17" s="3">
         <v>16400</v>
@@ -1237,8 +1237,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-28600</v>
       </c>
       <c r="E18" s="3">
         <v>-15700</v>
@@ -1315,8 +1315,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>200</v>
       </c>
       <c r="E20" s="3">
         <v>1700</v>
@@ -1371,8 +1371,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-27400</v>
       </c>
       <c r="E21" s="3">
         <v>-12300</v>
@@ -1651,8 +1651,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-29700</v>
       </c>
       <c r="E26" s="3">
         <v>-14000</v>
@@ -1707,8 +1707,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-29700</v>
       </c>
       <c r="E27" s="3">
         <v>-14000</v>
@@ -1987,8 +1987,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
         <v>-1700</v>
@@ -2043,8 +2043,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-29700</v>
       </c>
       <c r="E33" s="3">
         <v>-14000</v>
@@ -2155,8 +2155,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-29700</v>
       </c>
       <c r="E35" s="3">
         <v>-14000</v>
@@ -3201,25 +3201,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>7100</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4174,8 +4174,8 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>3</v>
+      <c r="D76" s="3">
+        <v>8100</v>
       </c>
       <c r="E76" s="3">
         <v>27200</v>
@@ -4347,8 +4347,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-29700</v>
       </c>
       <c r="E81" s="3">
         <v>-14000</v>
@@ -5008,7 +5008,7 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-109300</v>
+        <v>11700</v>
       </c>
       <c r="E94" s="3">
         <v>30100</v>

--- a/AAII_Financials/Quarterly/ASTR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASTR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
   <si>
     <t>ASTR</t>
   </si>
@@ -656,95 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -752,43 +759,43 @@
         <v>300</v>
       </c>
       <c r="E8" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F8" s="3">
+        <v>300</v>
+      </c>
+      <c r="G8" s="3">
         <v>700</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>2800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>3900</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -799,38 +806,44 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F9" s="3">
         <v>200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3">
         <v>1100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>17400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>11000</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,38 +868,44 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>300</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3">
         <v>1700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-14700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-7100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -911,8 +930,14 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,64 +958,72 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>18300</v>
+      </c>
+      <c r="F12" s="3">
         <v>21700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>24400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>31100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>29100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>32800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>40800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>37900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>36200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>21700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>22400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>12000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>27500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>7200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>8300</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,55 +1078,61 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>28900</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>1800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>133400</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>134400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>133800</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
@@ -1101,8 +1140,14 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,8 +1202,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1227,134 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>62500</v>
+      </c>
+      <c r="F17" s="3">
         <v>28900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>16400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>46500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>50300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>202500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>85300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>90200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>57500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>42400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>188900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>158400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>73500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>11100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>11400</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-59600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-28600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-15700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-46500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-50300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-199700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-82600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-86300</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3">
         <v>-188900</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-11400</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,132 +1375,146 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>6000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>300</v>
       </c>
       <c r="J20" s="3">
         <v>600</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="K20" s="3">
+        <v>300</v>
+      </c>
+      <c r="L20" s="3">
         <v>600</v>
       </c>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="O20" s="3">
+        <v>600</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>3500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-85100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-27400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-12300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-43500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-43000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-194700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-77400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-82900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-186500</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-10100</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F22" s="3">
         <v>1300</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1454,88 +1533,100 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3">
         <v>1900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>1100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>5700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>1300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>1000</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-89700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-29700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-14000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-44900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-44300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-199100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-82300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-85700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-51300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-16600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-190300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-159000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-68300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-12000</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1564,14 +1655,14 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1581,17 +1672,23 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1743,138 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-89700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-29700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-14000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-44900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-44300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-199100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-82300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-85700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-51300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-16200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-190300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-159000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-68300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-12000</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-89700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-29700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-14000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-44900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-44300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-199100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-82300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-85700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-51300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-16200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1202000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1170700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-68300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-12000</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1929,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1991,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +2053,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2115,138 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-62500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>27900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-6000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-300</v>
       </c>
       <c r="J32" s="3">
         <v>-600</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="K32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="O32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-89700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-29700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-14000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-44900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-44300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-199100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-82300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-85700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-51300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-16200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1202000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1170700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-68300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-12000</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2301,143 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-89700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-29700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-14000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-44900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-44300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-199100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-82300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-85700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-51300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-16200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1202000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1170700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-68300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-12000</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2458,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,50 +2482,52 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F41" s="3">
         <v>13900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>13400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>16800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>33600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>67600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>104300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>161500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>325000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>378700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>447500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>22500</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,38 +2540,44 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>12900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>45900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>69200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>82900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>96400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>93700</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2408,11 +2587,11 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2423,41 +2602,47 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F43" s="3">
         <v>1600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>5500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>6800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>5300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>4900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1800</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2467,11 +2652,11 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -2479,50 +2664,56 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F44" s="3">
         <v>13700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>11200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>6900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>6800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>3200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>8700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>7700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1000</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2535,50 +2726,56 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F45" s="3">
         <v>20800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>15800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>12400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>10800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>7600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>11200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>12200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>15200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>10300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>4700</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2591,50 +2788,56 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>31400</v>
+      </c>
+      <c r="F46" s="3">
         <v>49900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>58900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>88900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>125800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>168300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>211200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>275600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>346700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>398900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>459600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>28300</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,8 +2850,14 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2697,56 +2906,62 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>36300</v>
+      </c>
+      <c r="F48" s="3">
         <v>39600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>39400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>38300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>37100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>35000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>96800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>88400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>75400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>53000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>38900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>26500</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2759,50 +2974,56 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F49" s="3">
         <v>8400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>9000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>9600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>10100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>10700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>74500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>75400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>76200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>78200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>3200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3200</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,8 +3036,14 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +3098,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,8 +3160,14 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2939,38 +3178,38 @@
         <v>1800</v>
       </c>
       <c r="F52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H52" s="3">
         <v>1900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>2000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2983,8 +3222,14 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,50 +3284,56 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>78200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>77400</v>
+      </c>
+      <c r="F54" s="3">
         <v>99800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>109100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>138700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>174700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>215900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>385700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>439900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>499000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>530300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>501800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>58000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3095,8 +3346,14 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3374,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,50 +3398,52 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F57" s="3">
         <v>7100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>7200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>6900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>9300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>14300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>6200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>9100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>4900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>6200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3300</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3195,20 +3456,26 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>63500</v>
+      </c>
+      <c r="F58" s="3">
         <v>7100</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3221,24 +3488,24 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>4900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>3800</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3251,50 +3518,56 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>51600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>63000</v>
+      </c>
+      <c r="F59" s="3">
         <v>62500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>58600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>77700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>79700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>63700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>46900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>31100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>31600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>30400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>7200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>7700</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3307,50 +3580,56 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>85200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>131300</v>
+      </c>
+      <c r="F60" s="3">
         <v>76600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>65800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>84600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>81500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>73100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>61300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>37300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>40700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>35300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>18200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>14800</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3363,8 +3642,14 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3399,14 +3684,14 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>6400</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3419,50 +3704,56 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>21600</v>
+      </c>
+      <c r="F62" s="3">
         <v>15100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>16200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>10900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>10800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>28800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>25500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>34100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>21800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>58000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>66600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3800</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3475,8 +3766,14 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3828,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3890,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,50 +3952,56 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>152900</v>
+      </c>
+      <c r="F66" s="3">
         <v>91700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>81900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>95400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>92400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>101800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>86800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>71400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>62500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>93400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>84800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>25100</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3699,8 +4014,14 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +4042,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +4100,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +4162,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3869,14 +4204,14 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>1342500</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -3889,8 +4224,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,50 +4286,56 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1960100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1998200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1908500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1878700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-1864700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1819800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1775500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-1576400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-1494100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1408400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1357100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-380300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1309600</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4001,8 +4348,14 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4410,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4472,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,50 +4534,56 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-75400</v>
+      </c>
+      <c r="F76" s="3">
         <v>8100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>27200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>43300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>82300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>114100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>298900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>368500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>436500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>436900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>417000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-1309600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4225,8 +4596,14 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4658,143 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-89700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-29700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-14000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-44900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-44300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-199100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-82300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-85700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-51300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-16200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1202000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1170700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-68300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-12000</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,64 +4815,72 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F83" s="3">
         <v>1000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>4400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>4900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>2800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>1400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>2000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>3300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>900</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4935,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4997,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +5059,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +5121,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +5183,76 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-18100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-33500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-36000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-40800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-42800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-43600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-48300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-34800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-44900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-34700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-13700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-32900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-11200</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,64 +5273,72 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-3200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-5000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-7600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-8000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-11100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-21800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-20000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-9900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-8500</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-1200</v>
       </c>
       <c r="P91" s="3">
         <v>-200</v>
       </c>
       <c r="Q91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5393,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5455,76 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>600</v>
+      </c>
+      <c r="F94" s="3">
         <v>11700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>30100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>18700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>6700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>5600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-14000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-115700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-19800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-29300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-12000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-3500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-2200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1200</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5545,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5136,8 +5603,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5665,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5727,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,64 +5789,76 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F100" s="3">
         <v>11800</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
-      </c>
-      <c r="H100" s="3">
-        <v>500</v>
-      </c>
-      <c r="I100" s="3">
-        <v>300</v>
       </c>
       <c r="J100" s="3">
         <v>500</v>
       </c>
       <c r="K100" s="3">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="L100" s="3">
         <v>500</v>
       </c>
       <c r="M100" s="3">
+        <v>900</v>
+      </c>
+      <c r="N100" s="3">
+        <v>500</v>
+      </c>
+      <c r="O100" s="3">
         <v>488400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>29100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>35100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>5400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>17000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5416,60 +5913,72 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="F102" s="3">
         <v>5500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-3400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-16800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-34000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-36700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-57200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-163500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-53600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-73700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>441800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>11900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>4600</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
